--- a/src/attributions/attributions_ig_traj_484.xlsx
+++ b/src/attributions/attributions_ig_traj_484.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG5"/>
+  <dimension ref="A1:GG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,19 +1568,19 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03442535457671645</v>
+        <v>-0.1668305237064283</v>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2182670459609618</v>
+        <v>0.07189852842938659</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1143832955586387</v>
+        <v>0.01076253509129596</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -1589,25 +1589,25 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.01838358167342647</v>
+        <v>-0.1198962302668148</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.05811834589057453</v>
+        <v>0.02687164067338427</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.001889732496166407</v>
+        <v>-0.05694051628035882</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1616,52 +1616,52 @@
         <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01416011993220665</v>
+        <v>0.01325062201057318</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1679359403701563</v>
+        <v>0.08821089887717351</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.03562829758590747</v>
+        <v>-0.07187449963616793</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.04648225225758647</v>
+        <v>0.06644776894775362</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.04083604882128948</v>
+        <v>-0.09183130993313954</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.1268638220804145</v>
+        <v>-0.1086987040130563</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1676,52 +1676,52 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.01905924629173834</v>
+        <v>0.01424103778009123</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.06377782389037803</v>
+        <v>-0.08011995089733155</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.07630858201542405</v>
+        <v>-0.05368004495688571</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.03818507964260716</v>
+        <v>-0.1052207725522186</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.3530766308360472</v>
+        <v>0.0293165752575512</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.541549996136789</v>
+        <v>-0.2205767664551614</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
@@ -1730,19 +1730,19 @@
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1634796637323112</v>
+        <v>-0.05118433818992792</v>
       </c>
       <c r="BD3" t="n">
         <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.02698136468125835</v>
+        <v>0.04165296152979642</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.06092847939886694</v>
+        <v>0.182870770640151</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,103 +1754,103 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.04608602159919486</v>
+        <v>0.1613341363395554</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.2530356824841057</v>
+        <v>0.03340337562855005</v>
       </c>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1449881209466137</v>
+        <v>-0.01004498990220606</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.01779190585904689</v>
+        <v>-0.09905187683179133</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.04775373448945196</v>
+        <v>0.0914720346838073</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1233752154919273</v>
+        <v>-0.07691464099890968</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.002286268598480553</v>
+        <v>0.09299370173567637</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.06413167662813925</v>
+        <v>-0.003881640665176133</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.06323188940172896</v>
+        <v>0.03479780081996352</v>
       </c>
       <c r="CI3" t="n">
         <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001580100982804294</v>
+        <v>-0.02018411334914203</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.01471538604693685</v>
+        <v>-0.05653801946614347</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.2374450849134288</v>
+        <v>-0.03395072411513581</v>
       </c>
       <c r="CR3" t="n">
         <v>-0</v>
@@ -1865,73 +1865,73 @@
         <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01087154471529396</v>
+        <v>0.07815078518241196</v>
       </c>
       <c r="CW3" t="n">
         <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.04324383991446967</v>
+        <v>-0.02096863006231201</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01513214313651698</v>
+        <v>-0.01061125725062499</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>-0.01076242878566388</v>
+        <v>0.01894420302002972</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.002756861936375317</v>
+        <v>0.0002586134407346568</v>
       </c>
       <c r="DH3" t="n">
         <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1326540132558651</v>
+        <v>0.08905308613006091</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
         <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1480106568137458</v>
+        <v>0.08564468648474582</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.05217661862735947</v>
+        <v>0.06642001290992626</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.04741500334327655</v>
+        <v>-0.07734707682245384</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
@@ -1940,25 +1940,25 @@
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.08510630783778698</v>
+        <v>-0.01633686500362202</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.07123073636064933</v>
+        <v>0.201373150574568</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.04537820442409581</v>
+        <v>-0.121225916412314</v>
       </c>
       <c r="EB3" t="n">
         <v>-0</v>
@@ -1967,58 +1967,58 @@
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.05821355359013301</v>
+        <v>0.06271434772032344</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.1088250151206514</v>
+        <v>0.03942002076493861</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0295390567219349</v>
+        <v>0.03853150963624048</v>
       </c>
       <c r="EK3" t="n">
         <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.07446356294530435</v>
+        <v>0.04664410477391847</v>
       </c>
       <c r="EP3" t="n">
         <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.01669078891289519</v>
+        <v>-0.01498101761453312</v>
       </c>
       <c r="ER3" t="n">
         <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1644261916277988</v>
+        <v>0.07415844642951205</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2027,49 +2027,49 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02792321163225335</v>
+        <v>0.07940984165481246</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.04276616884501446</v>
+        <v>-0.03481506748758319</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02355650584176437</v>
+        <v>0.01410506485555875</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.01337963365514319</v>
+        <v>0.2556182911465846</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.04223180367848891</v>
+        <v>0.07702922329148518</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.08404363258113622</v>
+        <v>-0.1136115686819078</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
@@ -2078,49 +2078,49 @@
         <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.01666165082720857</v>
+        <v>0.1509736617107574</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0008386009585747129</v>
+        <v>0.00218503527831946</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.006510783965198121</v>
+        <v>0.001547726561062963</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.04396697478506825</v>
+        <v>0.1542693214500253</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0.02687863487426656</v>
+        <v>-0.01682185576364453</v>
       </c>
       <c r="GB3" t="n">
         <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
         <v>0</v>
@@ -2132,24 +2132,24 @@
         <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.1997069690104532</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.09372454709143174</v>
+        <v>0.5599348785940536</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>-0.3147254396596962</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.05150110357191914</v>
+        <v>-0.09337962421365319</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2158,25 +2158,25 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2314977245486841</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.04442160435912353</v>
+        <v>0.3891342836625659</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>-0.3291541255339555</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0004257897987995061</v>
+        <v>-0.07275597715445337</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -2191,46 +2191,46 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.02559525935625422</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.108788834240615</v>
+        <v>0.09825390810325527</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.08628262024308356</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.002160251176197418</v>
+        <v>-0.05835405433019722</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z4" t="n">
         <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0.03544277523620529</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.1266744065553315</v>
+        <v>0.0435953759445054</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>-0.1182763187361815</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02010848845857807</v>
+        <v>0.03432632327541383</v>
       </c>
       <c r="AG4" t="n">
         <v>-0</v>
@@ -2239,31 +2239,31 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02816609115693182</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.01490292480425753</v>
+        <v>0.3269869563657591</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>-0.1316015916326787</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.01975555188097078</v>
+        <v>0.2493985277899971</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,22 +2272,22 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.03336403162894757</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.130150947853632</v>
+        <v>0.6660568507283262</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0.2908272017104637</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.1861954000201846</v>
+        <v>-0.2811943960747911</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,103 +2296,103 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.1207159847444906</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.02087784204866483</v>
+        <v>-0.08597422732761426</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>-0.08278702998451204</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.1119593945452708</v>
+        <v>-0.1423677090977827</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.01913473766573949</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.07477258932088117</v>
+        <v>-0.1234020050659021</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0.006653924000877842</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.1485303300897753</v>
+        <v>0.02244583669377633</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
-        <v>-0.005115650978763295</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.1098023840964199</v>
+        <v>0.2402195436970047</v>
       </c>
       <c r="BW4" t="n">
         <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>-0.1394621372361092</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.09533980796319706</v>
+        <v>-0.02826047122989553</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB4" t="n">
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="n">
-        <v>-0.0253224449253836</v>
+        <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.02781267380605353</v>
+        <v>-0.3157678622989077</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>0.2124645257737532</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01162189547588586</v>
+        <v>-0.00829970844583868</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
@@ -2401,31 +2401,31 @@
         <v>-0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.0287471487803283</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.0001039485897798076</v>
+        <v>-0.2465434486924014</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0</v>
+        <v>0.2416353468690448</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0276837189155162</v>
+        <v>0.1074990130397509</v>
       </c>
       <c r="CR4" t="n">
         <v>-0</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
@@ -2434,76 +2434,76 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0.01168335407976136</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.0331869322931131</v>
+        <v>-0.3118422752511157</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0</v>
+        <v>0.2237813749773142</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.01029057142497208</v>
+        <v>0.013272746459029</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.04142946086253905</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.07308533925766968</v>
+        <v>-0.1356242692509777</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0</v>
+        <v>-0.01254582649903552</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.02261554825124901</v>
+        <v>0.002967773852174702</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0.004688975270188128</v>
+        <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.05634047148967482</v>
+        <v>-0.1492889207577053</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0</v>
+        <v>0.1035071806095272</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.04159319115348156</v>
+        <v>-0.08103038173069756</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
@@ -2512,22 +2512,22 @@
         <v>-0</v>
       </c>
       <c r="DV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>-0.03064678752620842</v>
+        <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.106987583541049</v>
+        <v>0.1104773760749926</v>
       </c>
       <c r="DY4" t="n">
         <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0</v>
+        <v>0.1134278285137283</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.05891538134248971</v>
+        <v>0.0759618591115596</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
@@ -2536,139 +2536,139 @@
         <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.02145074406716358</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0303855346837259</v>
+        <v>-0.2644816460921172</v>
       </c>
       <c r="EH4" t="n">
         <v>0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>0.1660429128966894</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.01407582478445989</v>
+        <v>0.06278578754586857</v>
       </c>
       <c r="EK4" t="n">
         <v>-0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
         <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.04306486915803701</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.01891541421667597</v>
+        <v>-0.1972070907214244</v>
       </c>
       <c r="EQ4" t="n">
         <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0.09576493171683211</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.07333871368747079</v>
+        <v>0.03037475306540331</v>
       </c>
       <c r="ET4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0.02125800049572997</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.03376822579713681</v>
+        <v>-0.351604128684951</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>0.2498479042582507</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.03082494039596912</v>
+        <v>-0.004546618166757672</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>-0.00536893247309096</v>
+        <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0005863164874417138</v>
+        <v>-0.1709604214796438</v>
       </c>
       <c r="FI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0</v>
+        <v>0.1527251630085118</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.08490742260533977</v>
+        <v>0.0292612793750518</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO4" t="n">
         <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>-0.03441545341535564</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.138233542879605</v>
+        <v>0.02491630996281225</v>
       </c>
       <c r="FR4" t="n">
         <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>0.26353792245123</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.1489209678209961</v>
+        <v>-0.001324499475421143</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
         <v>-0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.05764810296912738</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.004567870300908093</v>
+        <v>-0.2566760692267364</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0</v>
+        <v>0.1545443068712116</v>
       </c>
       <c r="GC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.4891930504234414</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0</v>
+        <v>0.08575293479933668</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.2644225856783849</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.409113903065824</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,25 +2745,25 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0</v>
+        <v>-0.04888151372697259</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.1013342757465575</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.1320300175017356</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0</v>
+        <v>-0.1495278963506745</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.03596033440874691</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-0.0003171278606603178</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -2799,16 +2799,16 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0</v>
+        <v>-0.2850543388767292</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0.06801732976518084</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.1519663643911125</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,16 +2826,16 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0</v>
+        <v>0.07243832534574415</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0.07284739075375982</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.5700409134598403</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2853,16 +2853,16 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0</v>
+        <v>-0.1805043498078748</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0.2027368344333917</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>0.1172016208798309</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,16 +2880,16 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0</v>
+        <v>-0.06352055163538163</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0.2075573239486599</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
@@ -2898,19 +2898,19 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>-0.02884031512832526</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0</v>
+        <v>0.06217468173087871</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>0.04273005915507228</v>
       </c>
       <c r="BR5" t="n">
         <v>0</v>
@@ -2922,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>0.1996321189150609</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,37 +2934,37 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0</v>
+        <v>0.006351286683014728</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0.06561514502518463</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>-0.1883174440413081</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0</v>
+        <v>-0.07684467850696415</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>0.1363789416228381</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,64 +2976,64 @@
         <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>-0.1731940987631232</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0</v>
+        <v>0.0719681453377789</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>0.1103456278071812</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>-0.180036363920248</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>-0.063125382252886</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>0.1425419849631439</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>-0.09011852980973828</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
@@ -3042,10 +3042,10 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0</v>
+        <v>-0.1993220130449512</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>0.06016090706073871</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3060,61 +3060,61 @@
         <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>-0.1137856443781208</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0</v>
+        <v>0.007979092535137894</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.1268671436345543</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>-0.04531709769908109</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0</v>
+        <v>0.1393661194142659</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>0.143208903076588</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>-0.09161460780680815</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
@@ -3123,40 +3123,40 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>-0.1035248647468562</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>0.03777705091922782</v>
       </c>
       <c r="EL5" t="n">
         <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>-0.08857214193894355</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0</v>
+        <v>-0.1466576240703542</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>0.201087437673674</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
         <v>0</v>
@@ -3165,22 +3165,22 @@
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>-0.202699142436098</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0</v>
+        <v>-0.1060056005072899</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>0.1220924835581452</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3189,25 +3189,25 @@
         <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>-0.2771676481804958</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0</v>
+        <v>0.05314978365099905</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>0.1961189766420106</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
@@ -3219,57 +3219,4609 @@
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>0.01668589044352231</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0</v>
+        <v>0.005361641246425233</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>0.06659393715103541</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW5" t="n">
         <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
         <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>-0.02815153758774522</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>0.1011636594051871</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7073413202431634</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.02216239850855012</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.1848723218896562</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5970689249178965</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.1428217789637891</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0.276567797528269</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.06435487157558888</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-0.1117645150627748</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.02022720226366129</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.06130669186561445</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>-0.1231458314391332</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.1979083430329339</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.3240184422212765</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-0.1204093275688065</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1507494886648682</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.5360104406336029</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>-0.04326219815756555</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0.2467278110921188</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.0645821843611301</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>-0.03760619762611231</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0.2282043810560452</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0.07182051534735281</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>-0.0491772023767079</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.09453287211572499</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.2162265960909215</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>-0.08860517258388996</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0.02653531773242799</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0.2977597794991323</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.06653180680912883</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.01050773563026914</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0.3200521756715373</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.2318855208438115</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.07393085523425671</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>-0.2846570174013825</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.06728908703294985</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.02228642178093504</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.1132114425014532</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-0.004850331802551881</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.04286923305964124</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0.1825700151571973</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.03902552631252144</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.03434144631174395</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.03206287207593832</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.07450833563260278</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.2454535185866344</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0.1718130317288422</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.0231577507265816</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0.01121899818165188</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0.1671847777282316</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.0389049458482176</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.02006051678958191</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0.3255123160727346</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.07036009418703039</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0.003996036713373808</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0.2717177840538977</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.124273746265798</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.1530271839908534</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.06934487257528241</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.2119870285740093</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.01340722375233249</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>-0.1265333773539739</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>-0.09130454510286237</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4550670581204432</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00577438209134954</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.246209894544606</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4571469145469176</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.1154370047824565</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.07428336757037052</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1250400176295358</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.08117444838747549</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.01135171104930701</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.06886408986002587</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.2359280499257</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.002814452490383689</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1688409776727529</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.02133931893662069</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.09905536288344341</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.5647662578777242</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.1672165397724202</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0.1894900925920394</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.02984407504789985</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.1700877349191152</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>-0.1407960095149896</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0179027208706065</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.08257811930570362</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.08854975636258698</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2009845155309225</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.01194226492933103</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>-0.0456222126194983</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.1479315033438217</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.007263019882018745</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.1128520219242944</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.2080242638562644</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.257100048840431</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.03269803755315632</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.1358980632001855</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.004107690164240452</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.1243103155524947</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.1389888947221284</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.1369198627960411</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.1048028959322065</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.1033577965963976</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.007191820340414099</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.06212491876112131</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>-0.002684876856986678</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.01334906037410059</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.06425327392489556</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06203036869110373</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.03306647619303441</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0140174945848099</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.09762146519488224</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.1277131936718099</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0.1920513247766666</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.1677853337887455</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.01525993578701821</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.1100640043397079</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.1350525604187148</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.1174249780406611</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.04850108890294048</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.02602493121991109</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.02398573510943876</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>-0.02497503480652588</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.0791179191785206</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.0538825351849015</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.4384577084443499</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4044706692820139</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.07727224489371906</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.3671445813756061</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4834324963633724</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1204732614378798</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-0.0660986545019825</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.06850009320118891</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01910163196130409</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.03447464115156147</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.01504713290768715</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.0341913240620885</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>-0.2470891244374113</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.04412447412012385</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-0.2014478600937132</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>-0.2216624534930238</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.2052678038000882</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.2610088440046502</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.05089336606787066</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.1328935019271846</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.1261352901440325</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.1407437996281325</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.05565231863504137</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.07374543073761222</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>-0.2398770579513618</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.1199303839657489</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.01827093959846937</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.2509202009262953</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0.1541434243093983</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.002921668162327694</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.1349919693971751</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0.3421405082917443</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>-0.1754440170409974</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.2512840577435386</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>-0.1519630076084328</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.01904803539473379</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.1369901660138532</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>-0.05987220019186048</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.06094976014476042</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.1051832894997714</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>-0.07476344585005178</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.05884193082468239</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.04431573374189991</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>-0.100730285515072</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>-0.08890635363477216</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.2046006290930193</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>-0.1071127605736455</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.05671659727369847</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.2026380489772476</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.06585943961142039</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.08220122401544903</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.2695122186452813</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0.1904983196641207</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.001306868682972859</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.1475153060842108</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0.1095958191296934</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>-0.0001095759262463921</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>-0.1298007066296544</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0.2667317327669908</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.006348933299651382</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.1780019723614711</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0.1348114296974721</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.3532512011380895</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.05949857472587756</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.201379005836149</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.3618116671554523</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.04853737303956405</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.1758039684655894</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.07085089247929131</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.008859878406012506</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.01336415532357989</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.0006737036493927625</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.116749416934158</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0.02729241615755097</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.05985645757285386</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0351465085119947</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-0.04530108179272234</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.3034772700735061</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.1101987314840799</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>-0.0994883841499683</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.04075195967992255</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.01510724958109111</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>-0.0517220535821918</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.002106538602970995</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.08271143504893293</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.04137228194202311</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.1460682623559655</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.01351713277068831</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>-0.06318029042661827</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.1083054557889831</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.003360691970404644</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.06877438599022968</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.0009340427711728521</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.04358531768582833</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.02865358199788428</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.1014296281352504</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>-0.003958116394270082</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.08576551515238612</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.02111967464097573</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.05471735907863676</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.04682920060986708</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.002296059197067339</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.06655342537897097</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0.05932087569955457</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>-0.08077321556747044</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.03005131478207321</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.004060696502781456</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.04520179752673653</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>-0.02904320003236044</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.04035669506078044</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.02704469008237458</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.00239536312036989</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.003036990764279984</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.1093886280922468</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.02670304772683129</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.0625010131390229</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.116580720728423</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.008321380134182019</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.1341748812440265</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>-0.1881828882785305</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.04412682758360714</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.082147274791774</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.03592893281961837</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.05326513556360039</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6425661707896092</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2905411100896974</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1795647579311852</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5245070888361781</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.4290830643640707</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.0455935512887238</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.05574307447607185</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.03034715922630392</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.008311339532639784</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.02716523719260633</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>-0.1842347452383682</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.1793568928253927</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1512140870209909</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-0.0576416334447308</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.2163031582699976</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.3428287476156191</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>-0.1914756859979773</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.09264709829724138</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.003215634405715898</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>-0.09177068130192377</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.007482767401587979</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>-0.08506262645992017</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0.07947855117554507</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>-0.05658458080981622</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.1510670385824494</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>-0.1188587285643172</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.01067775976008718</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1834428037266658</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.1074597600565255</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>-0.06185868006578909</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.07246314043134428</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.2291341960793411</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.1843210322156034</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.1831038238514044</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.1104918500511128</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.002198276660684576</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.04792624540141095</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.046132591312506</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.007741938377115951</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.1563473636215904</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.07773144105967258</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.02565707539408164</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.0410298617319927</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>-0.07177299074702909</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.09670577295341132</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.2009731239229877</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.1121034195220776</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.01729371775969014</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.1336018431291615</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0.05879074103445486</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.1180762602320656</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.222154886032986</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0.1229367188218984</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.05828543794209666</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.05537128025649265</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0.1364004085020559</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>-0.1108954434249809</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.2735179805832177</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0.05036175702008829</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.07461159456042178</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.1576176185259395</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0.000850956784214761</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.3395026015448797</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5.031951349659168e-05</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.1375987411705322</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3116027338226297</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.150273118281725</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0.2051877834276671</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.03456355767217349</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.03227011457483955</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.02549758402511463</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.02669716617710559</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.05909778891144793</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.09647983708093698</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.0412893496044962</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.0375131562887402</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.02135514439549495</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.1256104307242744</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.005310389798564583</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0.1122869878121553</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.1127501272889474</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.02715267139134464</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.07047526441116896</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0.05993342263963333</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.154309370633205</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.04613003827270573</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.05848808710617623</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.09802971521207755</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0.05682214246312278</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0.07974596159020114</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.0357180108896093</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.04092891997628759</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0.02830392360850174</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.2036461302788827</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0.09116718205522145</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0.08828320624860436</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.03822012176900542</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.05532172916999099</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0.002293309109758107</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.01222602261182273</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.02021265861381678</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>-0.03832120989353538</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.008711802460212317</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.07290878640664013</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0.0007401236901088175</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.2134900589116847</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.04103592815788894</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>-0.003985438414683904</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.01278295147820323</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.05479012062848418</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.06427839405037968</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.04933995629361376</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.01532645209140761</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0.07920273255707154</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.03974485033865238</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.05466035745958849</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>-0.09904359305157003</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.0004306745533487138</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.01996063254442207</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0.1517896920271032</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.007813253424440746</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.1436246770624217</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.02881906034122671</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.03089850698238748</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
         <v>0</v>
       </c>
     </row>
